--- a/src/nodes/LPC/compressor_stage_2_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/LPC/compressor_stage_2_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.0012394846175045778</v>
       </c>
       <c r="B2">
-        <v>0.00086972395081676807</v>
+        <v>0.00096144581251210665</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0024789692350091555</v>
       </c>
       <c r="B3">
-        <v>0.0014311569719689054</v>
+        <v>0.0015575844029543722</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0037184538525137337</v>
       </c>
       <c r="B4">
-        <v>0.0019300828514854569</v>
+        <v>0.0020832831502090227</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.004957938470018311</v>
       </c>
       <c r="B5">
-        <v>0.0023804732182074588</v>
+        <v>0.002555240549275604</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0061974230875228888</v>
       </c>
       <c r="B6">
-        <v>0.0027881945961434891</v>
+        <v>0.0029804340513629487</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0074369077050274674</v>
       </c>
       <c r="B7">
-        <v>0.003156695856065937</v>
+        <v>0.0033629460964186985</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0086763923225320443</v>
       </c>
       <c r="B8">
-        <v>0.0034881032855433244</v>
+        <v>0.0037052749688060971</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.009915876940036622</v>
       </c>
       <c r="B9">
-        <v>0.0037855639208373652</v>
+        <v>0.0040111501212231979</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0111553615575412</v>
       </c>
       <c r="B10">
-        <v>0.00405244290054382</v>
+        <v>0.00428456565752331</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.012394846175045778</v>
       </c>
       <c r="B11">
-        <v>0.00429195702390148</v>
+        <v>0.0045293431178459569</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.013634330792550357</v>
       </c>
       <c r="B12">
-        <v>0.0045058983815634288</v>
+        <v>0.00474759700017866</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.014873815410054935</v>
       </c>
       <c r="B13">
-        <v>0.0046905085691969104</v>
+        <v>0.0049347861976147128</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.016113300027559511</v>
       </c>
       <c r="B14">
-        <v>0.004843588197491192</v>
+        <v>0.0050882429232505721</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.017352784645064089</v>
       </c>
       <c r="B15">
-        <v>0.0049747244322095006</v>
+        <v>0.0052194482750896045</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.018592269262568666</v>
       </c>
       <c r="B16">
-        <v>0.0050927098531421272</v>
+        <v>0.00533893193865153</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.019831753880073244</v>
       </c>
       <c r="B17">
-        <v>0.0051913721411136577</v>
+        <v>0.0054392690646145733</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.021071238497577825</v>
       </c>
       <c r="B18">
-        <v>0.0052627024317087176</v>
+        <v>0.0055108335557619665</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.0223107231150824</v>
       </c>
       <c r="B19">
-        <v>0.0053063105785177795</v>
+        <v>0.0055531488581384483</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.023550207732586977</v>
       </c>
       <c r="B20">
-        <v>0.0053237111146327808</v>
+        <v>0.0055680258036041362</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.024789692350091555</v>
       </c>
       <c r="B21">
-        <v>0.0053164185731456575</v>
+        <v>0.0055572752240191457</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.026029176967596133</v>
       </c>
       <c r="B22">
-        <v>0.0052856730709731183</v>
+        <v>0.0055223808104977144</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.027268661585100714</v>
       </c>
       <c r="B23">
-        <v>0.0052316170603309677</v>
+        <v>0.0054635176911705524</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.028508146202605292</v>
       </c>
       <c r="B24">
-        <v>0.0051541185772597852</v>
+        <v>0.0053805338534224905</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.02974763082010987</v>
       </c>
       <c r="B25">
-        <v>0.0050530456578001468</v>
+        <v>0.00527327728463836</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.030987115437614444</v>
       </c>
       <c r="B26">
-        <v>0.0049282123403648712</v>
+        <v>0.0051415333136747851</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.032226600055119022</v>
       </c>
       <c r="B27">
-        <v>0.0047792166728557262</v>
+        <v>0.0049848366352755746</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.0334660846726236</v>
       </c>
       <c r="B28">
-        <v>0.00460560270554672</v>
+        <v>0.0048026592856563292</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.034705569290128177</v>
       </c>
       <c r="B29">
-        <v>0.0044069144887118614</v>
+        <v>0.0045944733010326536</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.035945053907632758</v>
       </c>
       <c r="B30">
-        <v>0.0041828810573015926</v>
+        <v>0.0043599750404400813</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.037184538525137333</v>
       </c>
       <c r="B31">
-        <v>0.0039339713849720886</v>
+        <v>0.0040997581541938758</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.038424023142641914</v>
       </c>
       <c r="B32">
-        <v>0.0036608394300559578</v>
+        <v>0.0038146406154292278</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.039663507760146488</v>
       </c>
       <c r="B33">
-        <v>0.0033641391508858081</v>
+        <v>0.00350544039728133</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.040902992377651069</v>
       </c>
       <c r="B34">
-        <v>0.0030441929605882823</v>
+        <v>0.003172580450573313</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.04214247699515565</v>
       </c>
       <c r="B35">
-        <v>0.0026999970914661532</v>
+        <v>0.0028149036368800492</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.043381961612660225</v>
       </c>
       <c r="B36">
-        <v>0.0023302162306162275</v>
+        <v>0.0024308577954643509</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.0446214462301648</v>
       </c>
       <c r="B37">
-        <v>0.001933515065135308</v>
+        <v>0.0020188907655890233</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.04586093084766938</v>
       </c>
       <c r="B38">
-        <v>0.001507764514950861</v>
+        <v>0.0015765008935989464</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.047100415465173955</v>
       </c>
       <c r="B39">
-        <v>0.001047660431312987</v>
+        <v>0.0010973885541672706</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.048339900082678536</v>
       </c>
       <c r="B40">
-        <v>0.00054710489830244585</v>
+        <v>0.00057430462904921461</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.048339900082678536</v>
       </c>
       <c r="B43">
-        <v>0.00027510759083475912</v>
+        <v>0.00024790786008799048</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.047100415465173955</v>
       </c>
       <c r="B44">
-        <v>0.00055037920277015129</v>
+        <v>0.00050065107991586783</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.04586093084766938</v>
       </c>
       <c r="B45">
-        <v>0.00082040072847000621</v>
+        <v>0.00075166434982192076</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.0446214462301648</v>
       </c>
       <c r="B46">
-        <v>0.0010797580605981549</v>
+        <v>0.00099438236014443948</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.043381961612660225</v>
       </c>
       <c r="B47">
-        <v>0.0013238005821349951</v>
+        <v>0.0012231590172868715</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.04214247699515565</v>
       </c>
       <c r="B48">
-        <v>0.0015509316373271914</v>
+        <v>0.001436025091913295</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.040902992377651069</v>
       </c>
       <c r="B49">
-        <v>0.0017603180607379792</v>
+        <v>0.0016319305707529486</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.039663507760146488</v>
       </c>
       <c r="B50">
-        <v>0.0019511266869305897</v>
+        <v>0.0018098254405350676</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.038424023142641914</v>
       </c>
       <c r="B51">
-        <v>0.0021228275763232559</v>
+        <v>0.0019690263909499859</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.037184538525137333</v>
       </c>
       <c r="B52">
-        <v>0.0022761036927542132</v>
+        <v>0.0021103169235324255</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.035945053907632758</v>
       </c>
       <c r="B53">
-        <v>0.0024119412259166937</v>
+        <v>0.0022348472427782041</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.034705569290128177</v>
       </c>
       <c r="B54">
-        <v>0.0025313263655039348</v>
+        <v>0.0023437675531831422</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.0334660846726236</v>
       </c>
       <c r="B55">
-        <v>0.0026350369044506198</v>
+        <v>0.00243798032434101</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.032226600055119022</v>
       </c>
       <c r="B56">
-        <v>0.0027230170486572357</v>
+        <v>0.0025173970862373872</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.030987115437614444</v>
       </c>
       <c r="B57">
-        <v>0.0027950026072657216</v>
+        <v>0.0025816816339558069</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.02974763082010987</v>
       </c>
       <c r="B58">
-        <v>0.0028507293894180132</v>
+        <v>0.0026304977625798</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.028508146202605292</v>
       </c>
       <c r="B59">
-        <v>0.002889965815632718</v>
+        <v>0.0026635505394700114</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.027268661585100714</v>
       </c>
       <c r="B60">
-        <v>0.0029126107519351135</v>
+        <v>0.0026807101210955283</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.026029176967596133</v>
       </c>
       <c r="B61">
-        <v>0.0029185956757271461</v>
+        <v>0.0026818879362025491</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.024789692350091555</v>
       </c>
       <c r="B62">
-        <v>0.0029078520644107613</v>
+        <v>0.0026669954135372723</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.023550207732586977</v>
       </c>
       <c r="B63">
-        <v>0.0028805642249192273</v>
+        <v>0.0026362495359478723</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.0223107231150824</v>
       </c>
       <c r="B64">
-        <v>0.0028379277823110931</v>
+        <v>0.0025910895026904244</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.021071238497577825</v>
       </c>
       <c r="B65">
-        <v>0.0027813911911762283</v>
+        <v>0.0025332600671229793</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.019831753880073244</v>
       </c>
       <c r="B66">
-        <v>0.0027124029061045027</v>
+        <v>0.0024645059826035871</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.018592269262568666</v>
       </c>
       <c r="B67">
-        <v>0.0026304889980481</v>
+        <v>0.0023842669125386977</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.017352784645064089</v>
       </c>
       <c r="B68">
-        <v>0.0025274860034084621</v>
+        <v>0.0022827621605283582</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.016113300027559511</v>
       </c>
       <c r="B69">
-        <v>0.0023970409398973908</v>
+        <v>0.0021523862141380112</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.014873815410054935</v>
       </c>
       <c r="B70">
-        <v>0.0022477322850188879</v>
+        <v>0.002003454656601086</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.013634330792550357</v>
       </c>
       <c r="B71">
-        <v>0.0020889121954111183</v>
+        <v>0.0018472135767958872</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.012394846175045778</v>
       </c>
       <c r="B72">
-        <v>0.0019180960844567125</v>
+        <v>0.0016807099905122359</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0111553615575412</v>
       </c>
       <c r="B73">
-        <v>0.0017312153307489245</v>
+        <v>0.0014990925737694352</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.009915876940036622</v>
       </c>
       <c r="B74">
-        <v>0.0015297019169790329</v>
+        <v>0.0013041157165932</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0086763923225320443</v>
       </c>
       <c r="B75">
-        <v>0.0013163864529156031</v>
+        <v>0.0010992147696528309</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0074369077050274674</v>
       </c>
       <c r="B76">
-        <v>0.0010941934525383191</v>
+        <v>0.0008879432121855573</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0061974230875228888</v>
       </c>
       <c r="B77">
-        <v>0.00086580004394888989</v>
+        <v>0.00067356058872943</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.004957938470018311</v>
       </c>
       <c r="B78">
-        <v>0.00063279990752600419</v>
+        <v>0.00045803257645785891</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0037184538525137337</v>
       </c>
       <c r="B79">
-        <v>0.00039807986424979876</v>
+        <v>0.00024487956552623303</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0024789692350091555</v>
       </c>
       <c r="B80">
-        <v>0.0001668826621142363</v>
+        <v>4.0455231128769449E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0012394846175045778</v>
       </c>
       <c r="B81">
-        <v>-4.7494666136619555E-05</v>
+        <v>-0.00013921652783195827</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0013433853529227439</v>
       </c>
       <c r="B2">
-        <v>0.0011477338833320769</v>
+        <v>0.0013465549155646428</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0026867707058454877</v>
       </c>
       <c r="B3">
-        <v>0.0018373220821287617</v>
+        <v>0.0021113726941250012</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0040301560587682316</v>
       </c>
       <c r="B4">
-        <v>0.0024415653800451236</v>
+        <v>0.0027736502392876256</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0053735414116909755</v>
       </c>
       <c r="B5">
-        <v>0.0029815336803647465</v>
+        <v>0.00336036834988896</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0067169267646137185</v>
       </c>
       <c r="B6">
-        <v>0.0034660081278779769</v>
+        <v>0.0038827162737452509</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0080603121175364632</v>
       </c>
       <c r="B7">
-        <v>0.0039001131111397716</v>
+        <v>0.0043471917565924608</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0094036974704592071</v>
       </c>
       <c r="B8">
-        <v>0.0042869717855950782</v>
+        <v>0.0047577243132902562</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.010747082823381951</v>
       </c>
       <c r="B9">
-        <v>0.0046312680987982942</v>
+        <v>0.0051202603672621735</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.012090468176304693</v>
       </c>
       <c r="B10">
-        <v>0.004938022539757129</v>
+        <v>0.0054411837850077433</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.013433853529227437</v>
       </c>
       <c r="B11">
-        <v>0.0052120409711831081</v>
+        <v>0.0057266112967666359</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.014777238882150183</v>
       </c>
       <c r="B12">
-        <v>0.005455972488771544</v>
+        <v>0.0059798908649802947</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.016120624235072926</v>
       </c>
       <c r="B13">
-        <v>0.0056640537464490845</v>
+        <v>0.0061935625171571137</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.017464009587995669</v>
       </c>
       <c r="B14">
-        <v>0.0058328918250536085</v>
+        <v>0.0063632180113844666</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.018807394940918414</v>
       </c>
       <c r="B15">
-        <v>0.005976987954836567</v>
+        <v>0.0065074639629987005</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.020150780293841156</v>
       </c>
       <c r="B16">
-        <v>0.0061096417602954792</v>
+        <v>0.006643365436359093</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.021494165646763902</v>
       </c>
       <c r="B17">
-        <v>0.0062214522934985828</v>
+        <v>0.0067588064346676786</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.022837550999686644</v>
       </c>
       <c r="B18">
-        <v>0.0063002370026660395</v>
+        <v>0.0068380988090166279</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.024180936352609386</v>
       </c>
       <c r="B19">
-        <v>0.0063453874930550023</v>
+        <v>0.0068804468632158895</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.025524321705532132</v>
       </c>
       <c r="B20">
-        <v>0.0063591889091818713</v>
+        <v>0.006888778014254862</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.026867707058454874</v>
       </c>
       <c r="B21">
-        <v>0.0063439263955630447</v>
+        <v>0.0068660196791229386</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.02821109241137762</v>
       </c>
       <c r="B22">
-        <v>0.00630147293783991</v>
+        <v>0.0068145728274391776</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.029554477764300365</v>
       </c>
       <c r="B23">
-        <v>0.006232052886153798</v>
+        <v>0.0067347326393412841</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.030897863117223107</v>
       </c>
       <c r="B24">
-        <v>0.0061354784317710328</v>
+        <v>0.0066262678475966222</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.032241248470145853</v>
       </c>
       <c r="B25">
-        <v>0.006011561765957932</v>
+        <v>0.0064889471849725582</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.033584633823068595</v>
       </c>
       <c r="B26">
-        <v>0.0058600373258631969</v>
+        <v>0.0063224428563048926</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.034928019175991337</v>
       </c>
       <c r="B27">
-        <v>0.0056803285321650439</v>
+        <v>0.006126040954703163</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.036271404528914079</v>
       </c>
       <c r="B28">
-        <v>0.0054717810514240692</v>
+        <v>0.0058989310453453443</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.037614789881836828</v>
       </c>
       <c r="B29">
-        <v>0.00523374055020087</v>
+        <v>0.0056403026934094087</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.038958175234759571</v>
       </c>
       <c r="B30">
-        <v>0.0049658379294171256</v>
+        <v>0.0053497159698206662</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.040301560587682313</v>
       </c>
       <c r="B31">
-        <v>0.0046688450274388485</v>
+        <v>0.0050282129684937685</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.041644945940605055</v>
       </c>
       <c r="B32">
-        <v>0.0043438189169931318</v>
+        <v>0.0046772062890907025</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.042988331293527804</v>
       </c>
       <c r="B33">
-        <v>0.0039918166708070683</v>
+        <v>0.0042981085312734542</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.044331716646450546</v>
       </c>
       <c r="B34">
-        <v>0.0036133977246639091</v>
+        <v>0.0038916970615151289</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.045675101999373288</v>
       </c>
       <c r="B35">
-        <v>0.0032071309665715289</v>
+        <v>0.0034562083135332967</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.04701848735229603</v>
       </c>
       <c r="B36">
-        <v>0.0027710876475939604</v>
+        <v>0.0029892434878566474</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.048361872705218772</v>
       </c>
       <c r="B37">
-        <v>0.002303339018795229</v>
+        <v>0.0024884037850138661</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.049705258058141522</v>
       </c>
       <c r="B38">
-        <v>0.0018007576370726594</v>
+        <v>0.001949754152212467</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.051048643411064264</v>
       </c>
       <c r="B39">
-        <v>0.0012554212826567433</v>
+        <v>0.0013632145233752643</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.052392028763987006</v>
       </c>
       <c r="B40">
-        <v>0.00065820904161126531</v>
+        <v>0.00071716857910389821</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.053735414116909748</v>
       </c>
       <c r="B42">
-        <v>1.1931658798072175E-17</v>
+        <v>1.1978266840252144E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.052392028763987006</v>
       </c>
       <c r="B43">
-        <v>0.0002454922791628352</v>
+        <v>0.00018653274167020211</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.051048643411064264</v>
       </c>
       <c r="B44">
-        <v>0.00050086859762709832</v>
+        <v>0.00039307535690857745</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.049705258058141522</v>
       </c>
       <c r="B45">
-        <v>0.00075778203109400707</v>
+        <v>0.00060878551595419975</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.048361872705218772</v>
       </c>
       <c r="B46">
-        <v>0.0010078856552647687</v>
+        <v>0.00082282088904613168</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.04701848735229603</v>
       </c>
       <c r="B47">
-        <v>0.0012439967657551507</v>
+        <v>0.0010258409254924636</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.045675101999373288</v>
       </c>
       <c r="B48">
-        <v>0.0014635895378391627</v>
+        <v>0.0012145121908773962</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.044331716646450546</v>
       </c>
       <c r="B49">
-        <v>0.0016653023667053788</v>
+        <v>0.00138700302985416</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.042988331293527804</v>
       </c>
       <c r="B50">
-        <v>0.0018477736475423694</v>
+        <v>0.0015414817870759837</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.041644945940605055</v>
       </c>
       <c r="B51">
-        <v>0.0020101073123101371</v>
+        <v>0.0016767199402125666</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.040301560587682313</v>
       </c>
       <c r="B52">
-        <v>0.0021532694400544093</v>
+        <v>0.0017939014989994892</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.038958175234759571</v>
       </c>
       <c r="B53">
-        <v>0.0022786916465923424</v>
+        <v>0.0018948136061888025</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.037614789881836828</v>
       </c>
       <c r="B54">
-        <v>0.0023878055477410966</v>
+        <v>0.0019812434045325573</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.036271404528914079</v>
       </c>
       <c r="B55">
-        <v>0.0024817310939751415</v>
+        <v>0.0020545811000538664</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.034928019175991337</v>
       </c>
       <c r="B56">
-        <v>0.0025603415743982055</v>
+        <v>0.0021146291518600855</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.033584633823068595</v>
       </c>
       <c r="B57">
-        <v>0.0026231986127713278</v>
+        <v>0.0021607930823296321</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.032241248470145853</v>
       </c>
       <c r="B58">
-        <v>0.0026698638328555495</v>
+        <v>0.0021924784138409232</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.030897863117223107</v>
       </c>
       <c r="B59">
-        <v>0.002699952520991904</v>
+        <v>0.0022091631051663141</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.029554477764300365</v>
       </c>
       <c r="B60">
-        <v>0.0027132946138413959</v>
+        <v>0.0022106148606539093</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.02821109241137762</v>
       </c>
       <c r="B61">
-        <v>0.0027097737106450215</v>
+        <v>0.0021966738210457523</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.026867707058454874</v>
       </c>
       <c r="B62">
-        <v>0.0026892734106437784</v>
+        <v>0.0021671801270838837</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.025524321705532132</v>
       </c>
       <c r="B63">
-        <v>0.0026520651736709265</v>
+        <v>0.0021224760685979349</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.024180936352609386</v>
       </c>
       <c r="B64">
-        <v>0.0025999719019287786</v>
+        <v>0.00206491253176789</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.022837550999686644</v>
       </c>
       <c r="B65">
-        <v>0.0025352043582119112</v>
+        <v>0.0019973425518613219</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.021494165646763902</v>
       </c>
       <c r="B66">
-        <v>0.0024599733053148995</v>
+        <v>0.0019226191641458024</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.020150780293841156</v>
       </c>
       <c r="B67">
-        <v>0.002373576027850181</v>
+        <v>0.0018398523517865672</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.018807394940918414</v>
       </c>
       <c r="B68">
-        <v>0.002263655897701636</v>
+        <v>0.0017331798895395031</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.017464009587995669</v>
       </c>
       <c r="B69">
-        <v>0.002120608520737611</v>
+        <v>0.0015902823344067542</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.016120624235072926</v>
       </c>
       <c r="B70">
-        <v>0.0019574923514928842</v>
+        <v>0.0014279835807848558</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.014777238882150183</v>
       </c>
       <c r="B71">
-        <v>0.0017885438553102836</v>
+        <v>0.0012646254791015327</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.013433853529227437</v>
       </c>
       <c r="B72">
-        <v>0.0016100486920984148</v>
+        <v>0.0010954783665148874</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.012090468176304693</v>
       </c>
       <c r="B73">
-        <v>0.0014158938230028357</v>
+        <v>0.00091273257775222267</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.010747082823381951</v>
       </c>
       <c r="B74">
-        <v>0.0012083222195511433</v>
+        <v>0.00071932995108726471</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0094036974704592071</v>
       </c>
       <c r="B75">
-        <v>0.00099170409172883128</v>
+        <v>0.00052095156403365341</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0080603121175364632</v>
       </c>
       <c r="B76">
-        <v>0.00077056259297094722</v>
+        <v>0.00032348394751825836</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0067169267646137185</v>
       </c>
       <c r="B77">
-        <v>0.00054905110680705707</v>
+        <v>0.00013234296093978312</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0053735414116909755</v>
       </c>
       <c r="B78">
-        <v>0.00032969099369525108</v>
+        <v>-4.9143675828962313E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0040301560587682316</v>
       </c>
       <c r="B79">
-        <v>0.00011697136534760715</v>
+        <v>-0.00021511349389489483</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0026867707058454877</v>
       </c>
       <c r="B80">
-        <v>-8.1032201844916167E-05</v>
+        <v>-0.00035508281384115571</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0013433853529227439</v>
       </c>
       <c r="B81">
-        <v>-0.00024401334229588582</v>
+        <v>-0.00044283437452845173</v>
       </c>
     </row>
     <row r="82" spans="1:2">
